--- a/converted_files/835/835-provider-level-adjustment.xlsx
+++ b/converted_files/835/835-provider-level-adjustment.xlsx
@@ -319,7 +319,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a68fd29aa71f5c1ede9185e</t>
+          <t>6aaac752fd84853fa5df822a</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a68fd29aa71f5c1ede9187e</t>
+          <t>6aaac752fd84853fa5df824a</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a68fd29aa71f5c1ede918a5</t>
+          <t>6aaac752fd84853fa5df8271</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -909,7 +909,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:BC7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1150,40 +1150,25 @@
       </c>
       <c r="AV1" s="3" t="inlineStr">
         <is>
-          <t>RemittanceDeliveryMethodReportTransmissionCode</t>
+          <t>ProviderIdentifier</t>
         </is>
       </c>
       <c r="AW1" s="3" t="inlineStr">
         <is>
-          <t>RemittanceDeliveryMethodName</t>
+          <t>FiscalPeriodDate</t>
         </is>
       </c>
       <c r="AX1" s="3" t="inlineStr">
         <is>
-          <t>RemittanceDeliveryMethodCommunicationNumber</t>
+          <t>ProviderAdjustmentReason</t>
         </is>
       </c>
       <c r="AY1" s="3" t="inlineStr">
         <is>
-          <t>ProviderIdentifier</t>
+          <t>ProviderAdjustmentReferenceIdentification</t>
         </is>
       </c>
       <c r="AZ1" s="3" t="inlineStr">
-        <is>
-          <t>FiscalPeriodDate</t>
-        </is>
-      </c>
-      <c r="BA1" s="3" t="inlineStr">
-        <is>
-          <t>ProviderAdjustmentReason</t>
-        </is>
-      </c>
-      <c r="BB1" s="3" t="inlineStr">
-        <is>
-          <t>ProviderAdjustmentReferenceIdentification</t>
-        </is>
-      </c>
-      <c r="BC1" s="3" t="inlineStr">
         <is>
           <t>ProviderAdjustmentAmount</t>
         </is>
@@ -1192,7 +1177,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a68fd29aa71f5c1ede9185e</t>
+          <t>6aaac752fd84853fa5df822a</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1240,70 +1225,171 @@
       <c r="L2" s="4" t="n">
         <v>45649.0</v>
       </c>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>ANY PLAN USA</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>1 WALK THIS WAY</t>
+        </is>
+      </c>
       <c r="Q2"/>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>ANYCITY</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>45209</t>
+        </is>
+      </c>
       <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
+        <is>
+          <t>8661112222</t>
+        </is>
+      </c>
       <c r="X2"/>
       <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
-      <c r="AD2"/>
-      <c r="AE2"/>
-      <c r="AF2"/>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>8002223333</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>EDI.SUPPORT@ANYPAYER.COM</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AF2" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
       <c r="AG2"/>
       <c r="AH2"/>
-      <c r="AI2"/>
-      <c r="AJ2"/>
-      <c r="AK2"/>
-      <c r="AL2"/>
-      <c r="AM2"/>
+      <c r="AI2" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="AJ2" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER1_NPI</t>
+        </is>
+      </c>
+      <c r="AK2" s="3" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="AL2" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER</t>
+        </is>
+      </c>
+      <c r="AM2" s="3" t="inlineStr">
+        <is>
+          <t>2255 ANY ROAD</t>
+        </is>
+      </c>
       <c r="AN2"/>
-      <c r="AO2"/>
-      <c r="AP2"/>
-      <c r="AQ2"/>
-      <c r="AR2"/>
-      <c r="AS2"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>ANY CITY</t>
+        </is>
+      </c>
+      <c r="AP2" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="AQ2" s="3" t="inlineStr">
+        <is>
+          <t>12211</t>
+        </is>
+      </c>
+      <c r="AR2" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID1</t>
+        </is>
+      </c>
       <c r="AT2"/>
       <c r="AU2"/>
-      <c r="AV2"/>
-      <c r="AW2"/>
-      <c r="AX2"/>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID1</t>
+        </is>
+      </c>
+      <c r="AW2" s="4" t="n">
+        <v>45657.0</v>
+      </c>
+      <c r="AX2" s="3" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
       <c r="AY2" s="3" t="inlineStr">
         <is>
-          <t>PAYEE_ID1</t>
-        </is>
-      </c>
-      <c r="AZ2" s="4" t="n">
-        <v>45657.0</v>
-      </c>
-      <c r="BA2" s="3" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="BB2" s="3" t="inlineStr">
-        <is>
           <t>3243079284</t>
         </is>
       </c>
-      <c r="BC2" s="1" t="n">
+      <c r="AZ2" s="1" t="n">
         <v>298.18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a68fd29aa71f5c1ede9185e</t>
+          <t>6aaac752fd84853fa5df822a</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1351,70 +1437,171 @@
       <c r="L3" s="4" t="n">
         <v>45649.0</v>
       </c>
-      <c r="M3"/>
-      <c r="N3"/>
-      <c r="O3"/>
-      <c r="P3"/>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>ANY PLAN USA</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>1 WALK THIS WAY</t>
+        </is>
+      </c>
       <c r="Q3"/>
-      <c r="R3"/>
-      <c r="S3"/>
-      <c r="T3"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>ANYCITY</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>45209</t>
+        </is>
+      </c>
       <c r="U3"/>
-      <c r="V3"/>
-      <c r="W3"/>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>8661112222</t>
+        </is>
+      </c>
       <c r="X3"/>
       <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3"/>
-      <c r="AB3"/>
-      <c r="AC3"/>
-      <c r="AD3"/>
-      <c r="AE3"/>
-      <c r="AF3"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>8002223333</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>EDI.SUPPORT@ANYPAYER.COM</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
       <c r="AG3"/>
       <c r="AH3"/>
-      <c r="AI3"/>
-      <c r="AJ3"/>
-      <c r="AK3"/>
-      <c r="AL3"/>
-      <c r="AM3"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER1_NPI</t>
+        </is>
+      </c>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>2255 ANY ROAD</t>
+        </is>
+      </c>
       <c r="AN3"/>
-      <c r="AO3"/>
-      <c r="AP3"/>
-      <c r="AQ3"/>
-      <c r="AR3"/>
-      <c r="AS3"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>ANY CITY</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>12211</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID1</t>
+        </is>
+      </c>
       <c r="AT3"/>
       <c r="AU3"/>
-      <c r="AV3"/>
-      <c r="AW3"/>
-      <c r="AX3"/>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID1</t>
+        </is>
+      </c>
+      <c r="AW3" s="4" t="n">
+        <v>45657.0</v>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="AY3" s="3" t="inlineStr">
         <is>
-          <t>PAYEE_ID1</t>
-        </is>
-      </c>
-      <c r="AZ3" s="4" t="n">
-        <v>45657.0</v>
-      </c>
-      <c r="BA3" s="3" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
           <t>3243079284</t>
         </is>
       </c>
-      <c r="BC3" s="1" t="n">
+      <c r="AZ3" s="1" t="n">
         <v>-298.18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a68fd29aa71f5c1ede9185e</t>
+          <t>6aaac752fd84853fa5df822a</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1462,70 +1649,171 @@
       <c r="L4" s="4" t="n">
         <v>45649.0</v>
       </c>
-      <c r="M4"/>
-      <c r="N4"/>
-      <c r="O4"/>
-      <c r="P4"/>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>ANY PLAN USA</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>1 WALK THIS WAY</t>
+        </is>
+      </c>
       <c r="Q4"/>
-      <c r="R4"/>
-      <c r="S4"/>
-      <c r="T4"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>ANYCITY</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>45209</t>
+        </is>
+      </c>
       <c r="U4"/>
-      <c r="V4"/>
-      <c r="W4"/>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>8661112222</t>
+        </is>
+      </c>
       <c r="X4"/>
       <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4"/>
-      <c r="AB4"/>
-      <c r="AC4"/>
-      <c r="AD4"/>
-      <c r="AE4"/>
-      <c r="AF4"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>8002223333</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>EDI.SUPPORT@ANYPAYER.COM</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
       <c r="AG4"/>
       <c r="AH4"/>
-      <c r="AI4"/>
-      <c r="AJ4"/>
-      <c r="AK4"/>
-      <c r="AL4"/>
-      <c r="AM4"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER1_NPI</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2255 ANY ROAD</t>
+        </is>
+      </c>
       <c r="AN4"/>
-      <c r="AO4"/>
-      <c r="AP4"/>
-      <c r="AQ4"/>
-      <c r="AR4"/>
-      <c r="AS4"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>ANY CITY</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>12211</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID1</t>
+        </is>
+      </c>
       <c r="AT4"/>
       <c r="AU4"/>
-      <c r="AV4"/>
-      <c r="AW4"/>
-      <c r="AX4"/>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID99</t>
+        </is>
+      </c>
+      <c r="AW4" s="4" t="n">
+        <v>45657.0</v>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
       <c r="AY4" s="3" t="inlineStr">
         <is>
-          <t>PAYEE_ID99</t>
-        </is>
-      </c>
-      <c r="AZ4" s="4" t="n">
-        <v>45657.0</v>
-      </c>
-      <c r="BA4" s="3" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="BB4" s="3" t="inlineStr">
-        <is>
           <t>3243079284</t>
         </is>
       </c>
-      <c r="BC4" s="1" t="n">
+      <c r="AZ4" s="1" t="n">
         <v>298.18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a68fd29aa71f5c1ede9185e</t>
+          <t>6aaac752fd84853fa5df822a</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1573,70 +1861,171 @@
       <c r="L5" s="4" t="n">
         <v>45649.0</v>
       </c>
-      <c r="M5"/>
-      <c r="N5"/>
-      <c r="O5"/>
-      <c r="P5"/>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>ANY PLAN USA</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>1 WALK THIS WAY</t>
+        </is>
+      </c>
       <c r="Q5"/>
-      <c r="R5"/>
-      <c r="S5"/>
-      <c r="T5"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>ANYCITY</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>45209</t>
+        </is>
+      </c>
       <c r="U5"/>
-      <c r="V5"/>
-      <c r="W5"/>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>8661112222</t>
+        </is>
+      </c>
       <c r="X5"/>
       <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5"/>
-      <c r="AB5"/>
-      <c r="AC5"/>
-      <c r="AD5"/>
-      <c r="AE5"/>
-      <c r="AF5"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>8002223333</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>EDI.SUPPORT@ANYPAYER.COM</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
       <c r="AG5"/>
       <c r="AH5"/>
-      <c r="AI5"/>
-      <c r="AJ5"/>
-      <c r="AK5"/>
-      <c r="AL5"/>
-      <c r="AM5"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER1_NPI</t>
+        </is>
+      </c>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>2255 ANY ROAD</t>
+        </is>
+      </c>
       <c r="AN5"/>
-      <c r="AO5"/>
-      <c r="AP5"/>
-      <c r="AQ5"/>
-      <c r="AR5"/>
-      <c r="AS5"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>ANY CITY</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>12211</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID1</t>
+        </is>
+      </c>
       <c r="AT5"/>
       <c r="AU5"/>
-      <c r="AV5"/>
-      <c r="AW5"/>
-      <c r="AX5"/>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID99</t>
+        </is>
+      </c>
+      <c r="AW5" s="4" t="n">
+        <v>45657.0</v>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="AY5" s="3" t="inlineStr">
         <is>
-          <t>PAYEE_ID99</t>
-        </is>
-      </c>
-      <c r="AZ5" s="4" t="n">
-        <v>45657.0</v>
-      </c>
-      <c r="BA5" s="3" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="BB5" s="3" t="inlineStr">
-        <is>
           <t>3243079284</t>
         </is>
       </c>
-      <c r="BC5" s="1" t="n">
+      <c r="AZ5" s="1" t="n">
         <v>-298.18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a68fd29aa71f5c1ede9187e</t>
+          <t>6aaac752fd84853fa5df824a</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1688,70 +2077,171 @@
       <c r="L6" s="4" t="n">
         <v>45649.0</v>
       </c>
-      <c r="M6"/>
-      <c r="N6"/>
-      <c r="O6"/>
-      <c r="P6"/>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>ANY PLAN USA</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>1 WALK THIS WAY</t>
+        </is>
+      </c>
       <c r="Q6"/>
-      <c r="R6"/>
-      <c r="S6"/>
-      <c r="T6"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>ANYCITY</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>45209</t>
+        </is>
+      </c>
       <c r="U6"/>
-      <c r="V6"/>
-      <c r="W6"/>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>8661112222</t>
+        </is>
+      </c>
       <c r="X6"/>
       <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6"/>
-      <c r="AB6"/>
-      <c r="AC6"/>
-      <c r="AD6"/>
-      <c r="AE6"/>
-      <c r="AF6"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>8002223333</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>EDI.SUPPORT@ANYPAYER.COM</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
       <c r="AG6"/>
       <c r="AH6"/>
-      <c r="AI6"/>
-      <c r="AJ6"/>
-      <c r="AK6"/>
-      <c r="AL6"/>
-      <c r="AM6"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER2_NPI</t>
+        </is>
+      </c>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>2255 ANY ROAD</t>
+        </is>
+      </c>
       <c r="AN6"/>
-      <c r="AO6"/>
-      <c r="AP6"/>
-      <c r="AQ6"/>
-      <c r="AR6"/>
-      <c r="AS6"/>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>ANY CITY</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr">
+        <is>
+          <t>12211</t>
+        </is>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID2</t>
+        </is>
+      </c>
       <c r="AT6"/>
       <c r="AU6"/>
-      <c r="AV6"/>
-      <c r="AW6"/>
-      <c r="AX6"/>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID2</t>
+        </is>
+      </c>
+      <c r="AW6" s="4" t="n">
+        <v>45291.0</v>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
       <c r="AY6" s="3" t="inlineStr">
         <is>
-          <t>PAYEE_ID2</t>
-        </is>
-      </c>
-      <c r="AZ6" s="4" t="n">
-        <v>45291.0</v>
-      </c>
-      <c r="BA6" s="3" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="BB6" s="3" t="inlineStr">
-        <is>
           <t>3243079284</t>
         </is>
       </c>
-      <c r="BC6" s="1" t="n">
+      <c r="AZ6" s="1" t="n">
         <v>298.18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a68fd29aa71f5c1ede918a5</t>
+          <t>6aaac752fd84853fa5df8271</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1799,63 +2289,164 @@
       <c r="L7" s="4" t="n">
         <v>45649.0</v>
       </c>
-      <c r="M7"/>
-      <c r="N7"/>
-      <c r="O7"/>
-      <c r="P7"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>ANY PLAN USA</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>1 WALK THIS WAY</t>
+        </is>
+      </c>
       <c r="Q7"/>
-      <c r="R7"/>
-      <c r="S7"/>
-      <c r="T7"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>ANYCITY</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>45209</t>
+        </is>
+      </c>
       <c r="U7"/>
-      <c r="V7"/>
-      <c r="W7"/>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>8661112222</t>
+        </is>
+      </c>
       <c r="X7"/>
       <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7"/>
-      <c r="AB7"/>
-      <c r="AC7"/>
-      <c r="AD7"/>
-      <c r="AE7"/>
-      <c r="AF7"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>8002223333</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>EDI.SUPPORT@ANYPAYER.COM</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
       <c r="AG7"/>
       <c r="AH7"/>
-      <c r="AI7"/>
-      <c r="AJ7"/>
-      <c r="AK7"/>
-      <c r="AL7"/>
-      <c r="AM7"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER3_NPI</t>
+        </is>
+      </c>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>2255 ANY ROAD</t>
+        </is>
+      </c>
       <c r="AN7"/>
-      <c r="AO7"/>
-      <c r="AP7"/>
-      <c r="AQ7"/>
-      <c r="AR7"/>
-      <c r="AS7"/>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>ANY CITY</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr">
+        <is>
+          <t>12211</t>
+        </is>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID3</t>
+        </is>
+      </c>
       <c r="AT7"/>
       <c r="AU7"/>
-      <c r="AV7"/>
-      <c r="AW7"/>
-      <c r="AX7"/>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID3</t>
+        </is>
+      </c>
+      <c r="AW7" s="4" t="n">
+        <v>44926.0</v>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
       <c r="AY7" s="3" t="inlineStr">
         <is>
-          <t>PAYEE_ID3</t>
-        </is>
-      </c>
-      <c r="AZ7" s="4" t="n">
-        <v>44926.0</v>
-      </c>
-      <c r="BA7" s="3" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="BB7" s="3" t="inlineStr">
-        <is>
           <t>3243079284</t>
         </is>
       </c>
-      <c r="BC7" s="1" t="n">
+      <c r="AZ7" s="1" t="n">
         <v>298.18</v>
       </c>
     </row>
@@ -2914,7 +3505,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a68fd29aa71f5c1ede918c7</t>
+          <t>6aaac752fd84853fa5df8299</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">

--- a/converted_files/835/835-provider-level-adjustment.xlsx
+++ b/converted_files/835/835-provider-level-adjustment.xlsx
@@ -6,9 +6,9 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Transactions" r:id="rId3" sheetId="1"/>
-    <sheet name="ProviderAdjustments" r:id="rId4" sheetId="2"/>
-    <sheet name="Service Lines" r:id="rId5" sheetId="3"/>
+    <sheet name="Remittances" r:id="rId3" sheetId="1"/>
+    <sheet name="Provider Adjustments" r:id="rId4" sheetId="2"/>
+    <sheet name="Claims and Service Lines" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
@@ -319,7 +319,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6aaac752fd84853fa5df822a</t>
+          <t>6ad90887b0eac4437b3058ca</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6aaac752fd84853fa5df824a</t>
+          <t>6ad90887b0eac4437b3058ea</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6aaac752fd84853fa5df8271</t>
+          <t>6ad90887b0eac4437b305911</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6aaac752fd84853fa5df822a</t>
+          <t>6ad90887b0eac4437b3058ca</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1389,7 +1389,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6aaac752fd84853fa5df822a</t>
+          <t>6ad90887b0eac4437b3058ca</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1601,7 +1601,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6aaac752fd84853fa5df822a</t>
+          <t>6ad90887b0eac4437b3058ca</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1813,7 +1813,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6aaac752fd84853fa5df822a</t>
+          <t>6ad90887b0eac4437b3058ca</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2025,7 +2025,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6aaac752fd84853fa5df824a</t>
+          <t>6ad90887b0eac4437b3058ea</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2241,7 +2241,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6aaac752fd84853fa5df8271</t>
+          <t>6ad90887b0eac4437b305911</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3505,7 +3505,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6aaac752fd84853fa5df8299</t>
+          <t>6ad90888b0eac4437b305939</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
